--- a/Code_for_grid_world/python_version/assignment/assignment2/results/stochastic/policy_matrix_stochastic.xlsx
+++ b/Code_for_grid_world/python_version/assignment/assignment2/results/stochastic/policy_matrix_stochastic.xlsx
@@ -549,19 +549,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -600,19 +600,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -685,19 +685,19 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07500000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
